--- a/history_prices/MAR/prices_12032026.xlsx
+++ b/history_prices/MAR/prices_12032026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E01793-3F6B-4ED6-BF01-539DB2B4B553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AB1D7F-88AC-4F83-91B5-34F932FD1EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,9 +342,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -355,12 +355,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -375,11 +381,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,19 +1216,19 @@
       <c r="B23" s="1">
         <v>46093</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1.3740000000000001</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="D23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.3740000000000001</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G23" s="6">
         <v>1.4039999999999999</v>
       </c>
     </row>
@@ -1230,19 +1239,19 @@
       <c r="B24" s="1">
         <v>46093</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="5">
         <v>1.3759999999999999</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="5">
         <v>0.09</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="6">
         <v>1.466</v>
       </c>
     </row>
@@ -1253,19 +1262,19 @@
       <c r="B25" s="1">
         <v>46093</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1.2290000000000001</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="D25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G25" s="6">
         <v>1.2589999999999999</v>
       </c>
     </row>
@@ -1276,19 +1285,19 @@
       <c r="B26" s="1">
         <v>46093</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="5">
         <v>1.4279999999999999</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="5">
         <v>0.09</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="6">
         <v>1.518</v>
       </c>
     </row>
